--- a/crud-generator/module.xlsx
+++ b/crud-generator/module.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F-03\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{026BF910-7728-4557-93A9-852C0EB0F69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9FA95F-9786-498F-AEEB-DA82F407BC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5CFB332-461D-47C8-B637-6D3B704974B7}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Model</t>
   </si>
@@ -51,16 +51,24 @@
     <t>users</t>
   </si>
   <si>
-    <t>name:string,email:string,password:string</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>products</t>
-  </si>
-  <si>
-    <t>name:string,price:decimal,stock:int</t>
+    <t>Indexes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>name:string(100),email:string:unique,password:string</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Song</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>songs</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>title:string,artist:string,album_id:foreign(albums.id),cover_image:string:nullable,audio_file:string:nullable</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -424,10 +432,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EA394E-56B0-4BC5-9E32-B0DE2ACFF0F7}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="91.5" customWidth="1"/>
+    <col min="4" max="4" width="33" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -437,8 +449,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -449,7 +464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -457,18 +472,18 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
